--- a/analysis_results.xlsx
+++ b/analysis_results.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Model_Metrics" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="LR_Odds_Ratios" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="LR_Model_Coefficients" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="DT_Feature_Importance" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Test_Predictions" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -540,25 +540,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Coefficient</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Odds_Ratio</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>CI_95_Lo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>CI_95_Hi</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Significant</t>
         </is>
@@ -567,46 +572,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sleep Time</t>
+          <t>Intercept</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.0713</v>
+        <v>-0.1367</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.4749</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3.6444</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>0.8722</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alcohol</t>
+          <t>Sleep Duration</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.2858</v>
+        <v>-0.2659</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1559</v>
+        <v>0.7665</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8868</v>
+        <v>0.1738</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1179</v>
-      </c>
-      <c r="F3" t="inlineStr">
+        <v>0.5105</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.1291</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -615,22 +620,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mental Fatigue</t>
+          <t>Screen Time</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.1569</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3951</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.75</v>
+        <v>0.909</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0723</v>
-      </c>
-      <c r="F4" t="inlineStr">
+        <v>0.6564</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.605</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -639,22 +647,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Caffeine</t>
+          <t>Night Screen</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.1272</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4444</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7903</v>
+        <v>0.5181</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7099</v>
-      </c>
-      <c r="F5" t="inlineStr">
+        <v>0.5452</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.3577</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -667,18 +678,21 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>0.0264</v>
+      </c>
+      <c r="C6" t="n">
         <v>1.0267</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>0.6545</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>0.7025</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>1.7543</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -687,22 +701,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Screen Time</t>
+          <t>Mental Fatigue</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0.1457</v>
       </c>
       <c r="C7" t="n">
-        <v>0.909</v>
+        <v>1.1569</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6564</v>
+        <v>0.3951</v>
       </c>
       <c r="E7" t="n">
-        <v>1.605</v>
-      </c>
-      <c r="F7" t="inlineStr">
+        <v>0.75</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.0723</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -715,18 +732,21 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
         <v>0.9112</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>0.6254999999999999</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>1.52</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -735,22 +755,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Night Screen</t>
+          <t>Caffeine</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0.1198</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5181</v>
+        <v>1.1272</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5452</v>
+        <v>0.4444</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3577</v>
-      </c>
-      <c r="F9" t="inlineStr">
+        <v>0.7903</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.7099</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -763,18 +786,21 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>-0.1274</v>
+      </c>
+      <c r="C10" t="n">
         <v>0.8804</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>0.4317</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>0.5279</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>1.3139</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -783,24 +809,54 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sleep Duration</t>
+          <t>Alcohol</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7665</v>
+        <v>0.2514</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1738</v>
+        <v>1.2858</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5105</v>
+        <v>0.1559</v>
       </c>
       <c r="E11" t="n">
-        <v>1.1291</v>
-      </c>
-      <c r="F11" t="inlineStr">
+        <v>0.8868</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.1179</v>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sleep Time</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.7282</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.0713</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.4749</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.6444</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
